--- a/results/tables/表1_各区域供需缺口与建设紧迫度.xlsx
+++ b/results/tables/表1_各区域供需缺口与建设紧迫度.xlsx
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.92673729515076</v>
+        <v>1.831255016922951</v>
       </c>
       <c r="E2" t="n">
-        <v>1410.561441262563</v>
+        <v>152.6045847435792</v>
       </c>
       <c r="F2" t="n">
         <v>3640</v>
@@ -535,20 +535,20 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2213.71337890625</v>
+        <v>245.369140625</v>
       </c>
       <c r="J2" t="n">
         <v>152000</v>
       </c>
       <c r="K2" t="n">
-        <v>1.456390380859375</v>
+        <v>0.1614270662006579</v>
       </c>
       <c r="L2" t="n">
-        <v>494.0968627929688</v>
+        <v>967.0794906616211</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>低风险</t>
+          <t>安全</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7.517253492355347</v>
+        <v>1.831255016922951</v>
       </c>
       <c r="E3" t="n">
-        <v>626.4377910296122</v>
+        <v>152.6045847435792</v>
       </c>
       <c r="F3" t="n">
         <v>4200</v>
@@ -588,16 +588,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>894.250244140625</v>
+        <v>245.369140625</v>
       </c>
       <c r="J3" t="n">
         <v>186000</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4807797011508737</v>
+        <v>0.1319188928091398</v>
       </c>
       <c r="L3" t="n">
-        <v>1175.075500488281</v>
+        <v>1169.079490661621</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         <v>25.03753485379281</v>
       </c>
       <c r="O3" t="n">
-        <v>90.65944910393472</v>
+        <v>91.8186674506637</v>
       </c>
     </row>
     <row r="4">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.220167894363403</v>
+        <v>1.857373454928398</v>
       </c>
       <c r="E4" t="n">
-        <v>685.0139911969503</v>
+        <v>154.7811212440332</v>
       </c>
       <c r="F4" t="n">
         <v>5500</v>
@@ -641,16 +641,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1135.307739257812</v>
+        <v>237.9653625488281</v>
       </c>
       <c r="J4" t="n">
         <v>255000</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4452187212775733</v>
+        <v>0.09331975001914827</v>
       </c>
       <c r="L4" t="n">
-        <v>1587.245820999146</v>
+        <v>1568.156406402588</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         <v>34.98833722092635</v>
       </c>
       <c r="O4" t="n">
-        <v>74.83928706550135</v>
+        <v>75.83955809962536</v>
       </c>
     </row>
     <row r="5">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.5820695605278</v>
+        <v>2.87657881873846</v>
       </c>
       <c r="E5" t="n">
-        <v>1298.50579671065</v>
+        <v>239.7149015615384</v>
       </c>
       <c r="F5" t="n">
         <v>7080</v>
@@ -694,16 +694,16 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1783.058837890625</v>
+        <v>283.1046142578125</v>
       </c>
       <c r="J5" t="n">
         <v>225000</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7924705946180557</v>
+        <v>0.1258242730034722</v>
       </c>
       <c r="L5" t="n">
-        <v>1336.69775390625</v>
+        <v>1421.001441955566</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>40.49937578027465</v>
       </c>
       <c r="O5" t="n">
-        <v>66.55551126043656</v>
+        <v>67.02479823921108</v>
       </c>
     </row>
     <row r="6">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.97770078277588</v>
+        <v>3.653258806228638</v>
       </c>
       <c r="E6" t="n">
-        <v>1498.14173189799</v>
+        <v>304.4382338523865</v>
       </c>
       <c r="F6" t="n">
         <v>10180</v>
@@ -747,16 +747,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1962.439331054688</v>
+        <v>294.4512023925781</v>
       </c>
       <c r="J6" t="n">
         <v>352000</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5575111735950818</v>
+        <v>0.08365090977061879</v>
       </c>
       <c r="L6" t="n">
-        <v>2027.5185546875</v>
+        <v>2089.764663696289</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>49.99545743617698</v>
       </c>
       <c r="O6" t="n">
-        <v>51.19648456510348</v>
+        <v>51.77242422322558</v>
       </c>
     </row>
     <row r="7">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.261790073394776</v>
+        <v>1.749226257532835</v>
       </c>
       <c r="E7" t="n">
-        <v>771.8158394495646</v>
+        <v>145.7688547944029</v>
       </c>
       <c r="F7" t="n">
         <v>4940</v>
@@ -800,16 +800,16 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>952.9539794921875</v>
+        <v>230.1560668945312</v>
       </c>
       <c r="J7" t="n">
         <v>205000</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4648555997522866</v>
+        <v>0.1122712521436737</v>
       </c>
       <c r="L7" t="n">
-        <v>1356.857391357422</v>
+        <v>1368.899917602539</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>65.02242152466367</v>
       </c>
       <c r="O7" t="n">
-        <v>27.25531800288391</v>
+        <v>27.69829454638019</v>
       </c>
     </row>
     <row r="8">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.18332241249085</v>
+        <v>3.055419787526131</v>
       </c>
       <c r="E8" t="n">
-        <v>1348.610201040903</v>
+        <v>254.6183156271776</v>
       </c>
       <c r="F8" t="n">
         <v>8860</v>
@@ -853,16 +853,16 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1758.646606445312</v>
+        <v>266.1549682617188</v>
       </c>
       <c r="J8" t="n">
         <v>308000</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5709891579367896</v>
+        <v>0.0864139507343243</v>
       </c>
       <c r="L8" t="n">
-        <v>1751.509902954102</v>
+        <v>1812.762954711914</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>69.7237017310253</v>
       </c>
       <c r="O8" t="n">
-        <v>19.94114482456702</v>
+        <v>20.14398627731859</v>
       </c>
     </row>
     <row r="9">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.39266575288773</v>
+        <v>3.098786395549774</v>
       </c>
       <c r="E9" t="n">
-        <v>1282.722146073977</v>
+        <v>258.2321996291478</v>
       </c>
       <c r="F9" t="n">
         <v>11100</v>
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2008.546997070312</v>
+        <v>275.9095458984375</v>
       </c>
       <c r="J9" t="n">
         <v>298000</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6740090594195678</v>
+        <v>0.09258709593907299</v>
       </c>
       <c r="L9" t="n">
-        <v>1659.383407592773</v>
+        <v>1711.513893127441</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>77.89473684210526</v>
       </c>
       <c r="O9" t="n">
-        <v>7.122717557848452</v>
+        <v>7.047394192342182</v>
       </c>
     </row>
     <row r="10">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.48824035525322</v>
+        <v>3.364210585594177</v>
       </c>
       <c r="E10" t="n">
-        <v>1374.020029604435</v>
+        <v>280.3508821328481</v>
       </c>
       <c r="F10" t="n">
         <v>12040</v>
@@ -959,16 +959,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1951.3349609375</v>
+        <v>288.5391845703125</v>
       </c>
       <c r="J10" t="n">
         <v>325000</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6004107572115385</v>
+        <v>0.08878128756009615</v>
       </c>
       <c r="L10" t="n">
-        <v>1818.215728759766</v>
+        <v>1898.229957580566</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>80.76036866359448</v>
       </c>
       <c r="O10" t="n">
-        <v>2.484316016713972</v>
+        <v>2.450469143896352</v>
       </c>
     </row>
     <row r="11">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.42457675504684</v>
+        <v>2.769789909601212</v>
       </c>
       <c r="E11" t="n">
-        <v>1035.381396253903</v>
+        <v>230.815825800101</v>
       </c>
       <c r="F11" t="n">
         <v>9240</v>
@@ -1012,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1540.460083007812</v>
+        <v>272.9317626953125</v>
       </c>
       <c r="J11" t="n">
         <v>276000</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5581377112347145</v>
+        <v>0.0988883198171422</v>
       </c>
       <c r="L11" t="n">
-        <v>1529.492408752441</v>
+        <v>1527.741188049316</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>

--- a/results/tables/表1_各区域供需缺口与建设紧迫度.xlsx
+++ b/results/tables/表1_各区域供需缺口与建设紧迫度.xlsx
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.831255016922951</v>
+        <v>16.20853424072266</v>
       </c>
       <c r="E2" t="n">
-        <v>152.6045847435792</v>
+        <v>1350.711181640625</v>
       </c>
       <c r="F2" t="n">
         <v>3640</v>
@@ -535,20 +535,20 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>245.369140625</v>
+        <v>1538.9375</v>
       </c>
       <c r="J2" t="n">
         <v>152000</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1614270662006579</v>
+        <v>1.012458881578947</v>
       </c>
       <c r="L2" t="n">
-        <v>967.0794906616211</v>
+        <v>-510.9375</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>高风险</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.831255016922951</v>
+        <v>23.23316383361816</v>
       </c>
       <c r="E3" t="n">
-        <v>152.6045847435792</v>
+        <v>1936.097005208333</v>
       </c>
       <c r="F3" t="n">
         <v>4200</v>
@@ -588,27 +588,27 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>245.369140625</v>
+        <v>1821.574096679688</v>
       </c>
       <c r="J3" t="n">
         <v>186000</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1319188928091398</v>
+        <v>0.9793409121933806</v>
       </c>
       <c r="L3" t="n">
-        <v>1169.079490661621</v>
+        <v>-266.303100585938</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>高风险</t>
         </is>
       </c>
       <c r="N3" t="n">
         <v>25.03753485379281</v>
       </c>
       <c r="O3" t="n">
-        <v>91.8186674506637</v>
+        <v>91.8742476730489</v>
       </c>
     </row>
     <row r="4">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.857373454928398</v>
+        <v>25.03522682189941</v>
       </c>
       <c r="E4" t="n">
-        <v>154.7811212440332</v>
+        <v>2086.268880208333</v>
       </c>
       <c r="F4" t="n">
         <v>5500</v>
@@ -641,27 +641,27 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>237.9653625488281</v>
+        <v>1781.177001953125</v>
       </c>
       <c r="J4" t="n">
         <v>255000</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09331975001914827</v>
+        <v>0.6985007850796568</v>
       </c>
       <c r="L4" t="n">
-        <v>1568.156406402588</v>
+        <v>-136.410522460938</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>中风险</t>
         </is>
       </c>
       <c r="N4" t="n">
         <v>34.98833722092635</v>
       </c>
       <c r="O4" t="n">
-        <v>75.83955809962536</v>
+        <v>75.6401375892426</v>
       </c>
     </row>
     <row r="5">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.87657881873846</v>
+        <v>19.87902450561523</v>
       </c>
       <c r="E5" t="n">
-        <v>239.7149015615384</v>
+        <v>1656.58544921875</v>
       </c>
       <c r="F5" t="n">
         <v>7080</v>
@@ -694,27 +694,27 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>283.1046142578125</v>
+        <v>2044.526977539062</v>
       </c>
       <c r="J5" t="n">
         <v>225000</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1258242730034722</v>
+        <v>0.9086786566840276</v>
       </c>
       <c r="L5" t="n">
-        <v>1421.001441955566</v>
+        <v>-203.09375</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>高风险</t>
         </is>
       </c>
       <c r="N5" t="n">
         <v>40.49937578027465</v>
       </c>
       <c r="O5" t="n">
-        <v>67.02479823921108</v>
+        <v>67.24367842258265</v>
       </c>
     </row>
     <row r="6">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.653258806228638</v>
+        <v>12.7493371963501</v>
       </c>
       <c r="E6" t="n">
-        <v>304.4382338523865</v>
+        <v>1062.444742838542</v>
       </c>
       <c r="F6" t="n">
         <v>10180</v>
@@ -747,16 +747,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>294.4512023925781</v>
+        <v>840.0941162109375</v>
       </c>
       <c r="J6" t="n">
         <v>352000</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08365090977061879</v>
+        <v>0.2386631011962891</v>
       </c>
       <c r="L6" t="n">
-        <v>2089.764663696289</v>
+        <v>1412.995971679688</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>49.99545743617698</v>
       </c>
       <c r="O6" t="n">
-        <v>51.77242422322558</v>
+        <v>51.09796795851582</v>
       </c>
     </row>
     <row r="7">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.749226257532835</v>
+        <v>6.033440113067627</v>
       </c>
       <c r="E7" t="n">
-        <v>145.7688547944029</v>
+        <v>502.7866617838542</v>
       </c>
       <c r="F7" t="n">
         <v>4940</v>
@@ -800,16 +800,16 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>230.1560668945312</v>
+        <v>554.9016723632812</v>
       </c>
       <c r="J7" t="n">
         <v>205000</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1122712521436737</v>
+        <v>0.2706837426162348</v>
       </c>
       <c r="L7" t="n">
-        <v>1368.899917602539</v>
+        <v>874.0983276367188</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>65.02242152466367</v>
       </c>
       <c r="O7" t="n">
-        <v>27.69829454638019</v>
+        <v>27.32382973748195</v>
       </c>
     </row>
     <row r="8">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.055419787526131</v>
+        <v>22.60712051391602</v>
       </c>
       <c r="E8" t="n">
-        <v>254.6183156271776</v>
+        <v>1883.9267578125</v>
       </c>
       <c r="F8" t="n">
         <v>8860</v>
@@ -853,16 +853,16 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>266.1549682617188</v>
+        <v>2046.7705078125</v>
       </c>
       <c r="J8" t="n">
         <v>308000</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0864139507343243</v>
+        <v>0.6645358791599025</v>
       </c>
       <c r="L8" t="n">
-        <v>1812.762954711914</v>
+        <v>779.604614257812</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>69.7237017310253</v>
       </c>
       <c r="O8" t="n">
-        <v>20.14398627731859</v>
+        <v>20.50984764092237</v>
       </c>
     </row>
     <row r="9">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.098786395549774</v>
+        <v>0.3547342419624329</v>
       </c>
       <c r="E9" t="n">
-        <v>258.2321996291478</v>
+        <v>29.56118774414062</v>
       </c>
       <c r="F9" t="n">
         <v>11100</v>
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>275.9095458984375</v>
+        <v>68.81431579589844</v>
       </c>
       <c r="J9" t="n">
         <v>298000</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09258709593907299</v>
+        <v>0.02309205228050283</v>
       </c>
       <c r="L9" t="n">
-        <v>1711.513893127441</v>
+        <v>1773.070419311523</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>77.89473684210526</v>
       </c>
       <c r="O9" t="n">
-        <v>7.047394192342182</v>
+        <v>6.511523056645673</v>
       </c>
     </row>
     <row r="10">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.364210585594177</v>
+        <v>1.718232154846191</v>
       </c>
       <c r="E10" t="n">
-        <v>280.3508821328481</v>
+        <v>143.1860148111979</v>
       </c>
       <c r="F10" t="n">
         <v>12040</v>
@@ -959,16 +959,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>288.5391845703125</v>
+        <v>207.1872711181641</v>
       </c>
       <c r="J10" t="n">
         <v>325000</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08878128756009615</v>
+        <v>0.06374992957481972</v>
       </c>
       <c r="L10" t="n">
-        <v>1898.229957580566</v>
+        <v>1868.846618652344</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>80.76036866359448</v>
       </c>
       <c r="O10" t="n">
-        <v>2.450469143896352</v>
+        <v>2.033973201080821</v>
       </c>
     </row>
     <row r="11">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.769789909601212</v>
+        <v>5.860442638397217</v>
       </c>
       <c r="E11" t="n">
-        <v>230.815825800101</v>
+        <v>488.3702392578125</v>
       </c>
       <c r="F11" t="n">
         <v>9240</v>
@@ -1012,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>272.9317626953125</v>
+        <v>848.1298828125</v>
       </c>
       <c r="J11" t="n">
         <v>276000</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0988883198171422</v>
+        <v>0.3072934358016304</v>
       </c>
       <c r="L11" t="n">
-        <v>1527.741188049316</v>
+        <v>1111.537719726562</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>

--- a/results/tables/表1_各区域供需缺口与建设紧迫度.xlsx
+++ b/results/tables/表1_各区域供需缺口与建设紧迫度.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.20853424072266</v>
+        <v>17.379</v>
       </c>
       <c r="E2" t="n">
-        <v>1350.711181640625</v>
+        <v>1448.25</v>
       </c>
       <c r="F2" t="n">
         <v>3640</v>
@@ -535,20 +535,20 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1538.9375</v>
+        <v>2360</v>
       </c>
       <c r="J2" t="n">
         <v>152000</v>
       </c>
       <c r="K2" t="n">
-        <v>1.012458881578947</v>
+        <v>1.552631578947369</v>
       </c>
       <c r="L2" t="n">
-        <v>-510.9375</v>
+        <v>111.3599999999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>高风险</t>
+          <t>低风险</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -564,7 +564,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.23316383361816</v>
+        <v>7.585</v>
       </c>
       <c r="E3" t="n">
-        <v>1936.097005208333</v>
+        <v>632.0833333333334</v>
       </c>
       <c r="F3" t="n">
         <v>4200</v>
@@ -588,27 +588,27 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1821.574096679688</v>
+        <v>806</v>
       </c>
       <c r="J3" t="n">
         <v>186000</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9793409121933806</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>-266.303100585938</v>
+        <v>1129.11</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>高风险</t>
+          <t>安全</t>
         </is>
       </c>
       <c r="N3" t="n">
         <v>25.03753485379281</v>
       </c>
       <c r="O3" t="n">
-        <v>91.8742476730489</v>
+        <v>91.56327705850764</v>
       </c>
     </row>
     <row r="4">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.03522682189941</v>
+        <v>7.788</v>
       </c>
       <c r="E4" t="n">
-        <v>2086.268880208333</v>
+        <v>649</v>
       </c>
       <c r="F4" t="n">
         <v>5500</v>
@@ -641,27 +641,27 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1781.177001953125</v>
+        <v>974</v>
       </c>
       <c r="J4" t="n">
         <v>255000</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6985007850796568</v>
+        <v>0.3819607843137255</v>
       </c>
       <c r="L4" t="n">
-        <v>-136.410522460938</v>
+        <v>1594.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>中风险</t>
+          <t>安全</t>
         </is>
       </c>
       <c r="N4" t="n">
         <v>34.98833722092635</v>
       </c>
       <c r="O4" t="n">
-        <v>75.6401375892426</v>
+        <v>75.62951859008319</v>
       </c>
     </row>
     <row r="5">
@@ -670,7 +670,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.87902450561523</v>
+        <v>15.916</v>
       </c>
       <c r="E5" t="n">
-        <v>1656.58544921875</v>
+        <v>1326.333333333333</v>
       </c>
       <c r="F5" t="n">
         <v>7080</v>
@@ -694,27 +694,27 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2044.526977539062</v>
+        <v>1927</v>
       </c>
       <c r="J5" t="n">
         <v>225000</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9086786566840276</v>
+        <v>0.8564444444444443</v>
       </c>
       <c r="L5" t="n">
-        <v>-203.09375</v>
+        <v>1348.16</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>高风险</t>
+          <t>安全</t>
         </is>
       </c>
       <c r="N5" t="n">
         <v>40.49937578027465</v>
       </c>
       <c r="O5" t="n">
-        <v>67.24367842258265</v>
+        <v>66.93604947306149</v>
       </c>
     </row>
     <row r="6">
@@ -723,19 +723,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>老城核心区</t>
+          <t>城市新区</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.7493371963501</v>
+        <v>17.634</v>
       </c>
       <c r="E6" t="n">
-        <v>1062.444742838542</v>
+        <v>1469.5</v>
       </c>
       <c r="F6" t="n">
         <v>10180</v>
@@ -747,16 +747,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>840.0941162109375</v>
+        <v>1814</v>
       </c>
       <c r="J6" t="n">
         <v>352000</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2386631011962891</v>
+        <v>0.5153409090909091</v>
       </c>
       <c r="L6" t="n">
-        <v>1412.995971679688</v>
+        <v>2053.42</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>49.99545743617698</v>
       </c>
       <c r="O6" t="n">
-        <v>51.09796795851582</v>
+        <v>51.65427733590759</v>
       </c>
     </row>
     <row r="7">
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.033440113067627</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>502.7866617838542</v>
+        <v>774.75</v>
       </c>
       <c r="F7" t="n">
         <v>4940</v>
@@ -800,16 +800,16 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>554.9016723632812</v>
+        <v>991</v>
       </c>
       <c r="J7" t="n">
         <v>205000</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2706837426162348</v>
+        <v>0.4834146341463415</v>
       </c>
       <c r="L7" t="n">
-        <v>874.0983276367188</v>
+        <v>1326.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>65.02242152466367</v>
       </c>
       <c r="O7" t="n">
-        <v>27.32382973748195</v>
+        <v>27.60419687203185</v>
       </c>
     </row>
     <row r="8">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22.60712051391602</v>
+        <v>15.733</v>
       </c>
       <c r="E8" t="n">
-        <v>1883.9267578125</v>
+        <v>1311.083333333333</v>
       </c>
       <c r="F8" t="n">
         <v>8860</v>
@@ -853,16 +853,16 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2046.7705078125</v>
+        <v>1726</v>
       </c>
       <c r="J8" t="n">
         <v>308000</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6645358791599025</v>
+        <v>0.5603896103896104</v>
       </c>
       <c r="L8" t="n">
-        <v>779.604614257812</v>
+        <v>1745.49</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>69.7237017310253</v>
       </c>
       <c r="O8" t="n">
-        <v>20.50984764092237</v>
+        <v>20.10264691752063</v>
       </c>
     </row>
     <row r="9">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3547342419624329</v>
+        <v>15.62</v>
       </c>
       <c r="E9" t="n">
-        <v>29.56118774414062</v>
+        <v>1301.666666666667</v>
       </c>
       <c r="F9" t="n">
         <v>11100</v>
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>68.81431579589844</v>
+        <v>1935</v>
       </c>
       <c r="J9" t="n">
         <v>298000</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02309205228050283</v>
+        <v>0.6493288590604026</v>
       </c>
       <c r="L9" t="n">
-        <v>1773.070419311523</v>
+        <v>1685.86</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>77.89473684210526</v>
       </c>
       <c r="O9" t="n">
-        <v>6.511523056645673</v>
+        <v>7.052927529135829</v>
       </c>
     </row>
     <row r="10">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.718232154846191</v>
+        <v>17.007</v>
       </c>
       <c r="E10" t="n">
-        <v>143.1860148111979</v>
+        <v>1417.25</v>
       </c>
       <c r="F10" t="n">
         <v>12040</v>
@@ -959,16 +959,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>207.1872711181641</v>
+        <v>2115</v>
       </c>
       <c r="J10" t="n">
         <v>325000</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06374992957481972</v>
+        <v>0.6507692307692308</v>
       </c>
       <c r="L10" t="n">
-        <v>1868.846618652344</v>
+        <v>1842.07</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>80.76036866359448</v>
       </c>
       <c r="O10" t="n">
-        <v>2.033973201080821</v>
+        <v>2.468556080669086</v>
       </c>
     </row>
     <row r="11">
@@ -993,14 +993,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>城市新区</t>
+          <t>老城核心区</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.860442638397217</v>
+        <v>12.314</v>
       </c>
       <c r="E11" t="n">
-        <v>488.3702392578125</v>
+        <v>1026.166666666667</v>
       </c>
       <c r="F11" t="n">
         <v>9240</v>
@@ -1012,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>848.1298828125</v>
+        <v>1619</v>
       </c>
       <c r="J11" t="n">
         <v>276000</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3072934358016304</v>
+        <v>0.5865942028985507</v>
       </c>
       <c r="L11" t="n">
-        <v>1111.537719726562</v>
+        <v>1517.99</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
